--- a/output/laminas_comunales/comunal_o_ocup_a_2023_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="C2">
-        <v>50.6044841735053</v>
+        <v>67.2733612273361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="C3">
-        <v>50.2977688307331</v>
+        <v>65.82798790827989</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>49.6229609110496</v>
+        <v>65.65802113352549</v>
       </c>
     </row>
     <row r="5">
@@ -429,7 +429,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>46.8392011385642</v>
+        <v>63.3022122634799</v>
       </c>
     </row>
     <row r="6">
@@ -444,67 +444,1192 @@
         </is>
       </c>
       <c r="C6">
-        <v>46.3708815046562</v>
+        <v>62.7766377143584</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C7">
-        <v>42.0405982905983</v>
+        <v>62.7237961514764</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="C8">
-        <v>39.5036926491409</v>
+        <v>62.4765654293213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="C9">
-        <v>37.2292614251679</v>
+        <v>62.4412668891413</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>60.3524577208788</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>60.2510460251046</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>59.9224927174365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>58.9411561046498</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>58.8645418326693</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>58.6504006501354</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>58.1342161795308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>57.4449433397477</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>57.4301295160191</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>57.3195996275605</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>2104</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Taltal</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C20">
+        <v>55.5997693194925</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>55.3255099189718</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>55.0658512118565</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>55.0505050505051</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>54.2512615291732</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>54.0809291123498</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>53.8891948837657</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>51.887077294686</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>51.6722703946204</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>51.5957446808511</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>50.6044841735053</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>50.2977688307331</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>49.6552568948621</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>49.6229609110496</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>48.8102568049463</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>48.5549888845299</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>46.8392011385642</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>46.5737167707951</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>46.3708815046562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>46.2547758367455</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>45.9636079789448</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>45.5284552845528</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>44.3453941618598</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>43.4191892370331</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>43.195847362514</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>42.0405982905983</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>41.9660100424874</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>41.6842064234487</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>41.4943903411356</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>39.8224670951944</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>39.5036926491409</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>39.3063583815029</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>39.264302507837</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>38.9276139410188</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>38.512236745221</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>38.4563024932992</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>38.3413402175441</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>38.1756756756757</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>37.9291647833238</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>37.4918756069399</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>37.4013528748591</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>37.3987253081809</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>37.2292614251679</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>37.0189775602007</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>36.9932671863926</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C65">
         <v>36.9618215271389</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>34.966867005702</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>31.744640861526</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>30.1373408855594</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>29.3632420638088</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>28.7580112643232</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>28.4331628926224</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>27.6902394797724</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>26.5249140893471</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ollagüe</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>26.1111111111111</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>23.3125864453665</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sierra Gorda</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>20.5439814814815</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>16.8865648032</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>16.7043808586811</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>16.614157439317</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>16.5091200478073</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>15.1348140781259</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Taltal</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>15.0209284627093</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tocopilla</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>13.4534905839833</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>11.3984674329502</v>
       </c>
     </row>
   </sheetData>
